--- a/public/player-import-template.xlsx
+++ b/public/player-import-template.xlsx
@@ -10,23 +10,6 @@
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <t>Keep this header row. Add one player per row below it. Blank cells stay empty. Import the Players sheet.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2320,7 +2303,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
